--- a/INFORMATYKA/EXCEL/Funkcje warunkowe/02_SumaWarunkow.xlsx
+++ b/INFORMATYKA/EXCEL/Funkcje warunkowe/02_SumaWarunkow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eseco-my.sharepoint.com/personal/admin_eseco_onmicrosoft_com/Documents/szkolenie_excel_zaaw_16godz/GOTOWE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stare\szkola26-27\INFORMATYKA\EXCEL\Funkcje warunkowe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{1F549586-7284-47CA-8725-08EDD587D50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C78EA58A-DD47-4232-BD41-FB2C28F0B57A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BA61B7-5AFD-450A-B895-F77F3010AFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D8D533CC-A1A3-4FEF-8070-A3BAB77DFF5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D8D533CC-A1A3-4FEF-8070-A3BAB77DFF5C}"/>
   </bookViews>
   <sheets>
     <sheet name="SumaJeżeli1" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="49">
   <si>
     <t>Data</t>
   </si>
@@ -199,7 +199,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;zł&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ _z_ł"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,8 +294,17 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,8 +346,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -413,6 +428,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -421,7 +445,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -434,7 +458,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -459,7 +482,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,6 +491,17 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Dane wyjściowe" xfId="3" builtinId="21"/>
@@ -1099,10 +1132,14 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1140,7 +1177,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1246,7 +1283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1388,7 +1425,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1407,206 +1444,275 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="10" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>120</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14">
+      <c r="D5" s="12">
+        <f>A5*C5</f>
+        <v>120</v>
+      </c>
+      <c r="E5" s="13">
         <v>0.23</v>
       </c>
-      <c r="F5" s="13"/>
+      <c r="F5" s="12">
+        <f>D5*(1+E5)</f>
+        <v>147.6</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>7</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>150</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14">
+      <c r="D6" s="12">
+        <f t="shared" ref="D6:D11" si="0">A6*C6</f>
+        <v>1050</v>
+      </c>
+      <c r="E6" s="13">
         <v>0.08</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="12">
+        <f t="shared" ref="F6:F11" si="1">D6*(1+E6)</f>
+        <v>1134</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>70</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14">
+      <c r="D7" s="12">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="E7" s="13">
         <v>0.03</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="12">
+        <f t="shared" si="1"/>
+        <v>216.3</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>50</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14">
+      <c r="D8" s="12">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E8" s="13">
         <v>0</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="12">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="10">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>74</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14">
+      <c r="D9" s="12">
+        <f t="shared" si="0"/>
+        <v>296</v>
+      </c>
+      <c r="E9" s="13">
         <v>0.08</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="12">
+        <f t="shared" si="1"/>
+        <v>319.68</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>120</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14">
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="E10" s="13">
         <v>0.23</v>
       </c>
-      <c r="F10" s="13"/>
+      <c r="F10" s="12">
+        <f t="shared" si="1"/>
+        <v>885.6</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>5</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>50</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14">
+      <c r="D11" s="12">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="E11" s="13">
         <v>0.23</v>
       </c>
-      <c r="F11" s="13"/>
+      <c r="F11" s="12">
+        <f t="shared" si="1"/>
+        <v>307.5</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="9"/>
+      <c r="D14" s="21">
+        <f>SUM(D5:D11)</f>
+        <v>2846</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="21">
+        <f>SUM(F5:F11)</f>
+        <v>3210.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="22"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>0.23</v>
       </c>
-      <c r="F16" s="9"/>
+      <c r="F16" s="21">
+        <f>SUMIF($E$5:$E$11,E16,$F$5:$F$11)</f>
+        <v>1340.7</v>
+      </c>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>0.08</v>
       </c>
-      <c r="F17" s="9"/>
+      <c r="F17" s="21">
+        <f t="shared" ref="F17:F19" si="2">SUMIF($E$5:$E$11,E17,$F$5:$F$11)</f>
+        <v>1453.68</v>
+      </c>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>0.03</v>
       </c>
-      <c r="F18" s="9"/>
+      <c r="F18" s="21">
+        <f t="shared" si="2"/>
+        <v>216.3</v>
+      </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>0</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="21">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="22"/>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="9"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="21">
+        <f>F14-D14</f>
+        <v>364.67999999999984</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1630,7 +1736,7 @@
     <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1706,16 +1812,16 @@
       <c r="E5" s="6">
         <v>3.25</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="24" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1735,7 +1841,20 @@
       <c r="E6" s="6">
         <v>8</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="30">
+        <f>SUMIF($B$3:$B$87,I6,$E$3:$E$87)</f>
+        <v>117.75</v>
+      </c>
+      <c r="K6" s="26">
+        <v>35</v>
+      </c>
+      <c r="L6" s="26">
+        <f>IF(K6="","",J6*K6)</f>
+        <v>4121.25</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1753,7 +1872,20 @@
       <c r="E7" s="6">
         <v>5</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="30">
+        <f t="shared" ref="J7:J10" si="0">SUMIF($B$3:$B$87,I7,$E$3:$E$87)</f>
+        <v>134.25</v>
+      </c>
+      <c r="K7" s="26">
+        <v>35</v>
+      </c>
+      <c r="L7" s="26">
+        <f t="shared" ref="L7:L10" si="1">IF(K7="","",J7*K7)</f>
+        <v>4698.75</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1771,7 +1903,20 @@
       <c r="E8" s="6">
         <v>3.5</v>
       </c>
-      <c r="I8" s="3"/>
+      <c r="I8" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="30">
+        <f t="shared" si="0"/>
+        <v>98.5</v>
+      </c>
+      <c r="K8" s="26">
+        <v>35</v>
+      </c>
+      <c r="L8" s="26">
+        <f t="shared" si="1"/>
+        <v>3447.5</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
@@ -1789,7 +1934,20 @@
       <c r="E9" s="6">
         <v>7.5</v>
       </c>
-      <c r="I9" s="4"/>
+      <c r="I9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="30">
+        <f t="shared" si="0"/>
+        <v>202.5</v>
+      </c>
+      <c r="K9" s="26">
+        <v>35</v>
+      </c>
+      <c r="L9" s="26">
+        <f t="shared" si="1"/>
+        <v>7087.5</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1807,7 +1965,20 @@
       <c r="E10" s="6">
         <v>4.25</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="30">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="K10" s="26">
+        <v>35</v>
+      </c>
+      <c r="L10" s="29">
+        <f t="shared" si="1"/>
+        <v>3675</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -3164,13 +3335,16 @@
       <c r="K2" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="19"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>36162</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="31">
+        <f>MONTH(A3)</f>
+        <v>1</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
@@ -3182,13 +3356,19 @@
       </c>
       <c r="F3" s="6">
         <v>4.75</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>36252</v>
       </c>
-      <c r="B4" s="8"/>
+      <c r="B4" s="31">
+        <f t="shared" ref="B4:B67" si="0">MONTH(A4)</f>
+        <v>4</v>
+      </c>
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
@@ -3212,7 +3392,10 @@
       <c r="A5" s="7">
         <v>36225</v>
       </c>
-      <c r="B5" s="8"/>
+      <c r="B5" s="31">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -3227,13 +3410,20 @@
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="K5" s="23">
+        <f>SUMIFS($F$3:$F$87,$C$3:$C$87,J5,$B$3:$B$87,$K$3)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>36282</v>
       </c>
-      <c r="B6" s="8"/>
+      <c r="B6" s="31">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
@@ -3248,13 +3438,20 @@
       </c>
       <c r="J6" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="K6" s="23">
+        <f t="shared" ref="K6:K9" si="1">SUMIFS($F$3:$F$87,$C$3:$C$87,J6,$B$3:$B$87,$K$3)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>36380</v>
       </c>
-      <c r="B7" s="8"/>
+      <c r="B7" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
@@ -3269,13 +3466,20 @@
       </c>
       <c r="J7" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="K7" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>36414</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
@@ -3290,13 +3494,20 @@
       </c>
       <c r="J8" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="K8" s="23">
+        <f t="shared" si="1"/>
+        <v>23.5</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>36384</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
@@ -3311,13 +3522,20 @@
       </c>
       <c r="J9" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="K9" s="23">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>36415</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
@@ -3335,7 +3553,10 @@
       <c r="A11" s="2">
         <v>36386</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
@@ -3353,7 +3574,10 @@
       <c r="A12" s="7">
         <v>36387</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
@@ -3371,7 +3595,10 @@
       <c r="A13" s="7">
         <v>36387</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
@@ -3389,7 +3616,10 @@
       <c r="A14" s="7">
         <v>36425</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
@@ -3407,7 +3637,10 @@
       <c r="A15" s="7">
         <v>36427</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
@@ -3425,7 +3658,10 @@
       <c r="A16" s="2">
         <v>36488</v>
       </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="31">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>13</v>
       </c>
@@ -3443,7 +3679,10 @@
       <c r="A17" s="2">
         <v>36400</v>
       </c>
-      <c r="B17" s="8"/>
+      <c r="B17" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>13</v>
       </c>
@@ -3461,7 +3700,10 @@
       <c r="A18" s="2">
         <v>36505</v>
       </c>
-      <c r="B18" s="8"/>
+      <c r="B18" s="31">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
@@ -3479,7 +3721,10 @@
       <c r="A19" s="7">
         <v>36193</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="31">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>8</v>
       </c>
@@ -3497,7 +3742,10 @@
       <c r="A20" s="2">
         <v>36375</v>
       </c>
-      <c r="B20" s="8"/>
+      <c r="B20" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>8</v>
       </c>
@@ -3515,7 +3763,10 @@
       <c r="A21" s="2">
         <v>36257</v>
       </c>
-      <c r="B21" s="8"/>
+      <c r="B21" s="31">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
       </c>
@@ -3533,7 +3784,10 @@
       <c r="A22" s="7">
         <v>36328</v>
       </c>
-      <c r="B22" s="8"/>
+      <c r="B22" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
       </c>
@@ -3551,7 +3805,10 @@
       <c r="A23" s="2">
         <v>36363</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="31">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
       </c>
@@ -3569,7 +3826,10 @@
       <c r="A24" s="2">
         <v>36381</v>
       </c>
-      <c r="B24" s="8"/>
+      <c r="B24" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
@@ -3587,7 +3847,10 @@
       <c r="A25" s="2">
         <v>36385</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
       </c>
@@ -3605,7 +3868,10 @@
       <c r="A26" s="2">
         <v>36418</v>
       </c>
-      <c r="B26" s="8"/>
+      <c r="B26" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
       </c>
@@ -3623,7 +3889,10 @@
       <c r="A27" s="7">
         <v>36448</v>
       </c>
-      <c r="B27" s="8"/>
+      <c r="B27" s="31">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="C27" s="3" t="s">
         <v>8</v>
       </c>
@@ -3641,7 +3910,10 @@
       <c r="A28" s="2">
         <v>36390</v>
       </c>
-      <c r="B28" s="8"/>
+      <c r="B28" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
       </c>
@@ -3659,7 +3931,10 @@
       <c r="A29" s="2">
         <v>36390</v>
       </c>
-      <c r="B29" s="8"/>
+      <c r="B29" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3677,7 +3952,10 @@
       <c r="A30" s="7">
         <v>36394</v>
       </c>
-      <c r="B30" s="8"/>
+      <c r="B30" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C30" s="3" t="s">
         <v>8</v>
       </c>
@@ -3695,7 +3973,10 @@
       <c r="A31" s="2">
         <v>36396</v>
       </c>
-      <c r="B31" s="8"/>
+      <c r="B31" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C31" s="3" t="s">
         <v>8</v>
       </c>
@@ -3713,7 +3994,10 @@
       <c r="A32" s="7">
         <v>36491</v>
       </c>
-      <c r="B32" s="8"/>
+      <c r="B32" s="31">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="C32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3731,7 +4015,10 @@
       <c r="A33" s="2">
         <v>36504</v>
       </c>
-      <c r="B33" s="8"/>
+      <c r="B33" s="31">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
       <c r="C33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3749,7 +4036,10 @@
       <c r="A34" s="7">
         <v>36162</v>
       </c>
-      <c r="B34" s="8"/>
+      <c r="B34" s="31">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="C34" s="3" t="s">
         <v>5</v>
       </c>
@@ -3767,7 +4057,10 @@
       <c r="A35" s="2">
         <v>36221</v>
       </c>
-      <c r="B35" s="8"/>
+      <c r="B35" s="31">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>5</v>
       </c>
@@ -3785,7 +4078,10 @@
       <c r="A36" s="2">
         <v>36295</v>
       </c>
-      <c r="B36" s="8"/>
+      <c r="B36" s="31">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>5</v>
       </c>
@@ -3803,7 +4099,10 @@
       <c r="A37" s="7">
         <v>36364</v>
       </c>
-      <c r="B37" s="8"/>
+      <c r="B37" s="31">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="C37" s="3" t="s">
         <v>5</v>
       </c>
@@ -3821,7 +4120,10 @@
       <c r="A38" s="2">
         <v>36357</v>
       </c>
-      <c r="B38" s="8"/>
+      <c r="B38" s="31">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="C38" s="3" t="s">
         <v>5</v>
       </c>
@@ -3839,7 +4141,10 @@
       <c r="A39" s="2">
         <v>36363</v>
       </c>
-      <c r="B39" s="8"/>
+      <c r="B39" s="31">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="C39" s="3" t="s">
         <v>5</v>
       </c>
@@ -3857,7 +4162,10 @@
       <c r="A40" s="2">
         <v>36364</v>
       </c>
-      <c r="B40" s="8"/>
+      <c r="B40" s="31">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="C40" s="3" t="s">
         <v>5</v>
       </c>
@@ -3875,7 +4183,10 @@
       <c r="A41" s="2">
         <v>36383</v>
       </c>
-      <c r="B41" s="8"/>
+      <c r="B41" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3893,7 +4204,10 @@
       <c r="A42" s="2">
         <v>36476</v>
       </c>
-      <c r="B42" s="8"/>
+      <c r="B42" s="31">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="C42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3911,7 +4225,10 @@
       <c r="A43" s="7">
         <v>36387</v>
       </c>
-      <c r="B43" s="8"/>
+      <c r="B43" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3929,7 +4246,10 @@
       <c r="A44" s="7">
         <v>36387</v>
       </c>
-      <c r="B44" s="8"/>
+      <c r="B44" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3947,7 +4267,10 @@
       <c r="A45" s="7">
         <v>36390</v>
       </c>
-      <c r="B45" s="8"/>
+      <c r="B45" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3965,7 +4288,10 @@
       <c r="A46" s="7">
         <v>36394</v>
       </c>
-      <c r="B46" s="8"/>
+      <c r="B46" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3983,7 +4309,10 @@
       <c r="A47" s="2">
         <v>36458</v>
       </c>
-      <c r="B47" s="8"/>
+      <c r="B47" s="31">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4001,7 +4330,10 @@
       <c r="A48" s="2">
         <v>36397</v>
       </c>
-      <c r="B48" s="8"/>
+      <c r="B48" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4019,7 +4351,10 @@
       <c r="A49" s="2">
         <v>36428</v>
       </c>
-      <c r="B49" s="8"/>
+      <c r="B49" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C49" s="4" t="s">
         <v>5</v>
       </c>
@@ -4037,7 +4372,10 @@
       <c r="A50" s="7">
         <v>36428</v>
       </c>
-      <c r="B50" s="8"/>
+      <c r="B50" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>5</v>
       </c>
@@ -4055,7 +4393,10 @@
       <c r="A51" s="2">
         <v>36400</v>
       </c>
-      <c r="B51" s="8"/>
+      <c r="B51" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>5</v>
       </c>
@@ -4073,7 +4414,10 @@
       <c r="A52" s="7">
         <v>36400</v>
       </c>
-      <c r="B52" s="8"/>
+      <c r="B52" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4091,7 +4435,10 @@
       <c r="A53" s="2">
         <v>36220</v>
       </c>
-      <c r="B53" s="8"/>
+      <c r="B53" s="31">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="C53" s="4" t="s">
         <v>10</v>
       </c>
@@ -4109,7 +4456,10 @@
       <c r="A54" s="7">
         <v>36291</v>
       </c>
-      <c r="B54" s="8"/>
+      <c r="B54" s="31">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="C54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4127,7 +4477,10 @@
       <c r="A55" s="7">
         <v>36333</v>
       </c>
-      <c r="B55" s="8"/>
+      <c r="B55" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="C55" s="3" t="s">
         <v>10</v>
       </c>
@@ -4145,7 +4498,10 @@
       <c r="A56" s="7">
         <v>36323</v>
       </c>
-      <c r="B56" s="8"/>
+      <c r="B56" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="C56" s="3" t="s">
         <v>10</v>
       </c>
@@ -4163,7 +4519,10 @@
       <c r="A57" s="7">
         <v>36325</v>
       </c>
-      <c r="B57" s="8"/>
+      <c r="B57" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="C57" s="4" t="s">
         <v>10</v>
       </c>
@@ -4181,7 +4540,10 @@
       <c r="A58" s="7">
         <v>36322</v>
       </c>
-      <c r="B58" s="8"/>
+      <c r="B58" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="C58" s="3" t="s">
         <v>10</v>
       </c>
@@ -4199,7 +4561,10 @@
       <c r="A59" s="7">
         <v>36411</v>
       </c>
-      <c r="B59" s="8"/>
+      <c r="B59" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4217,7 +4582,10 @@
       <c r="A60" s="2">
         <v>36505</v>
       </c>
-      <c r="B60" s="8"/>
+      <c r="B60" s="31">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4235,7 +4603,10 @@
       <c r="A61" s="2">
         <v>36384</v>
       </c>
-      <c r="B61" s="8"/>
+      <c r="B61" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C61" s="3" t="s">
         <v>10</v>
       </c>
@@ -4253,7 +4624,10 @@
       <c r="A62" s="2">
         <v>36386</v>
       </c>
-      <c r="B62" s="8"/>
+      <c r="B62" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C62" s="4" t="s">
         <v>10</v>
       </c>
@@ -4271,7 +4645,10 @@
       <c r="A63" s="7">
         <v>36387</v>
       </c>
-      <c r="B63" s="8"/>
+      <c r="B63" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>10</v>
       </c>
@@ -4289,7 +4666,10 @@
       <c r="A64" s="7">
         <v>36420</v>
       </c>
-      <c r="B64" s="8"/>
+      <c r="B64" s="31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="C64" s="4" t="s">
         <v>10</v>
       </c>
@@ -4307,7 +4687,10 @@
       <c r="A65" s="7">
         <v>36389</v>
       </c>
-      <c r="B65" s="8"/>
+      <c r="B65" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C65" s="3" t="s">
         <v>10</v>
       </c>
@@ -4325,7 +4708,10 @@
       <c r="A66" s="7">
         <v>36397</v>
       </c>
-      <c r="B66" s="8"/>
+      <c r="B66" s="31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4343,7 +4729,10 @@
       <c r="A67" s="7">
         <v>36490</v>
       </c>
-      <c r="B67" s="8"/>
+      <c r="B67" s="31">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
@@ -4361,7 +4750,10 @@
       <c r="A68" s="7">
         <v>36461</v>
       </c>
-      <c r="B68" s="8"/>
+      <c r="B68" s="31">
+        <f t="shared" ref="B68:B87" si="2">MONTH(A68)</f>
+        <v>10</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>10</v>
       </c>
@@ -4379,7 +4771,10 @@
       <c r="A69" s="7">
         <v>36221</v>
       </c>
-      <c r="B69" s="8"/>
+      <c r="B69" s="31">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
       <c r="C69" s="3" t="s">
         <v>9</v>
       </c>
@@ -4397,7 +4792,10 @@
       <c r="A70" s="2">
         <v>36346</v>
       </c>
-      <c r="B70" s="8"/>
+      <c r="B70" s="31">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="C70" s="3" t="s">
         <v>9</v>
       </c>
@@ -4415,7 +4813,10 @@
       <c r="A71" s="2">
         <v>36348</v>
       </c>
-      <c r="B71" s="8"/>
+      <c r="B71" s="31">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="C71" s="3" t="s">
         <v>9</v>
       </c>
@@ -4433,7 +4834,10 @@
       <c r="A72" s="7">
         <v>36380</v>
       </c>
-      <c r="B72" s="8"/>
+      <c r="B72" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C72" s="3" t="s">
         <v>9</v>
       </c>
@@ -4451,7 +4855,10 @@
       <c r="A73" s="7">
         <v>36506</v>
       </c>
-      <c r="B73" s="8"/>
+      <c r="B73" s="31">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
       <c r="C73" s="3" t="s">
         <v>9</v>
       </c>
@@ -4469,7 +4876,10 @@
       <c r="A74" s="7">
         <v>36387</v>
       </c>
-      <c r="B74" s="8"/>
+      <c r="B74" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C74" s="3" t="s">
         <v>9</v>
       </c>
@@ -4487,7 +4897,10 @@
       <c r="A75" s="7">
         <v>36418</v>
       </c>
-      <c r="B75" s="8"/>
+      <c r="B75" s="31">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="C75" s="3" t="s">
         <v>9</v>
       </c>
@@ -4505,7 +4918,10 @@
       <c r="A76" s="2">
         <v>36418</v>
       </c>
-      <c r="B76" s="8"/>
+      <c r="B76" s="31">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="C76" s="3" t="s">
         <v>9</v>
       </c>
@@ -4523,7 +4939,10 @@
       <c r="A77" s="7">
         <v>36389</v>
       </c>
-      <c r="B77" s="8"/>
+      <c r="B77" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C77" s="3" t="s">
         <v>9</v>
       </c>
@@ -4541,7 +4960,10 @@
       <c r="A78" s="7">
         <v>36390</v>
       </c>
-      <c r="B78" s="8"/>
+      <c r="B78" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C78" s="3" t="s">
         <v>9</v>
       </c>
@@ -4559,7 +4981,10 @@
       <c r="A79" s="7">
         <v>36390</v>
       </c>
-      <c r="B79" s="8"/>
+      <c r="B79" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C79" s="3" t="s">
         <v>9</v>
       </c>
@@ -4577,7 +5002,10 @@
       <c r="A80" s="7">
         <v>36390</v>
       </c>
-      <c r="B80" s="8"/>
+      <c r="B80" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C80" s="3" t="s">
         <v>9</v>
       </c>
@@ -4595,7 +5023,10 @@
       <c r="A81" s="2">
         <v>36391</v>
       </c>
-      <c r="B81" s="8"/>
+      <c r="B81" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C81" s="3" t="s">
         <v>9</v>
       </c>
@@ -4613,7 +5044,10 @@
       <c r="A82" s="2">
         <v>36393</v>
       </c>
-      <c r="B82" s="8"/>
+      <c r="B82" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C82" s="3" t="s">
         <v>9</v>
       </c>
@@ -4631,7 +5065,10 @@
       <c r="A83" s="7">
         <v>36455</v>
       </c>
-      <c r="B83" s="8"/>
+      <c r="B83" s="31">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
       <c r="C83" s="3" t="s">
         <v>9</v>
       </c>
@@ -4649,7 +5086,10 @@
       <c r="A84" s="7">
         <v>36395</v>
       </c>
-      <c r="B84" s="8"/>
+      <c r="B84" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C84" s="3" t="s">
         <v>9</v>
       </c>
@@ -4667,7 +5107,10 @@
       <c r="A85" s="2">
         <v>36397</v>
       </c>
-      <c r="B85" s="8"/>
+      <c r="B85" s="31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="C85" s="3" t="s">
         <v>9</v>
       </c>
@@ -4685,7 +5128,10 @@
       <c r="A86" s="7">
         <v>36492</v>
       </c>
-      <c r="B86" s="8"/>
+      <c r="B86" s="31">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
       <c r="C86" s="3" t="s">
         <v>9</v>
       </c>
@@ -4703,7 +5149,10 @@
       <c r="A87" s="7">
         <v>36431</v>
       </c>
-      <c r="B87" s="8"/>
+      <c r="B87" s="31">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="C87" s="3" t="s">
         <v>9</v>
       </c>
@@ -4718,6 +5167,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3" xr:uid="{E995D8AE-CDF6-43CA-A757-42EE1F710E33}">
+      <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
